--- a/artfynd/A 42868-2026 artfynd.xlsx
+++ b/artfynd/A 42868-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,9 +799,558 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137338733</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5188</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Vifallet, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>520057</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6536876</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137338733</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137338742</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58194</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vifallet, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>520070</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6536909</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137338742</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137338741</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58189</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vifallet, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>520070</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6536909</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137338741</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137338735</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5208</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vifallet, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>520057</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6536876</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137338735</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137338738</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5208</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vifallet, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>520092</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6536880</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137338738</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42868-2026 artfynd.xlsx
+++ b/artfynd/A 42868-2026 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>137338742</v>
       </c>
       <c r="B4" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>137338741</v>
       </c>
       <c r="B5" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42868-2026 artfynd.xlsx
+++ b/artfynd/A 42868-2026 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>137338742</v>
       </c>
       <c r="B4" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>137338741</v>
       </c>
       <c r="B5" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42868-2026 artfynd.xlsx
+++ b/artfynd/A 42868-2026 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>137338742</v>
       </c>
       <c r="B4" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>137338741</v>
       </c>
       <c r="B5" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
